--- a/verification/model_verification_results_118_buses_raw.xlsx
+++ b/verification/model_verification_results_118_buses_raw.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\verification\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1947FC-8C1B-4FC3-BDE6-AD5E92DDA773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>checkpoint_118_50_False_vr_vi_final.pt_0.00</t>
   </si>
@@ -145,16 +139,34 @@
     <t>Vm Up Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Up Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Up Avg Violation</t>
+  </si>
+  <si>
     <t>Vm Down Max Violation</t>
   </si>
   <si>
     <t>Vm Down Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Down Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Down Avg Violation</t>
+  </si>
+  <si>
     <t>Vm tot Max Violation</t>
   </si>
   <si>
     <t>Vm tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Avg Violation</t>
   </si>
   <si>
     <t>Ibal tot Max Violation</t>
@@ -166,8 +178,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,18 +196,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -225,36 +231,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -292,7 +286,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -326,7 +320,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -361,10 +354,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,22 +529,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="0" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="0" hidden="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Y29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -629,30 +610,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B2">
-        <v>2203375</v>
+        <v>2027047.875</v>
       </c>
       <c r="C2">
-        <v>2139052.25</v>
+        <v>2019291</v>
       </c>
       <c r="D2">
-        <v>2076991.25</v>
+        <v>2011222.625</v>
       </c>
       <c r="E2">
-        <v>2017952</v>
+        <v>2000436.5</v>
       </c>
       <c r="F2">
-        <v>2000301.625</v>
+        <v>1999940.75</v>
       </c>
       <c r="G2">
-        <v>1999472.125</v>
+        <v>1999470.875</v>
       </c>
       <c r="H2">
-        <v>1.960992813110352E-3</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -670,66 +651,66 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>30.882781982421879</v>
+        <v>26.44383239746094</v>
       </c>
       <c r="O2">
-        <v>22.908357620239261</v>
+        <v>20.32553100585938</v>
       </c>
       <c r="P2">
-        <v>15.28395938873291</v>
+        <v>14.35314750671387</v>
       </c>
       <c r="Q2">
-        <v>9.9349193572998047</v>
+        <v>9.646162986755371</v>
       </c>
       <c r="R2">
-        <v>7.1496262550354004</v>
+        <v>7.103845596313477</v>
       </c>
       <c r="S2">
-        <v>6.3218646049499512</v>
+        <v>6.321864604949951</v>
       </c>
       <c r="T2">
-        <v>7.6940097808837891</v>
+        <v>7.489950656890869</v>
       </c>
       <c r="U2">
-        <v>7.2213387489318848</v>
+        <v>7.185243129730225</v>
       </c>
       <c r="V2">
-        <v>6.9422745704650879</v>
+        <v>6.933363437652588</v>
       </c>
       <c r="W2">
-        <v>6.6859946250915527</v>
+        <v>6.681993007659912</v>
       </c>
       <c r="X2">
-        <v>6.4577927589416504</v>
+        <v>6.456469058990479</v>
       </c>
       <c r="Y2">
         <v>6.302091121673584</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B3">
-        <v>2035320.375</v>
+        <v>2003706.25</v>
       </c>
       <c r="C3">
-        <v>2023528</v>
+        <v>2003608</v>
       </c>
       <c r="D3">
-        <v>2012171.875</v>
+        <v>2002056</v>
       </c>
       <c r="E3">
-        <v>2001483.125</v>
+        <v>1999387.125</v>
       </c>
       <c r="F3">
-        <v>1998727.875</v>
+        <v>1998422.5</v>
       </c>
       <c r="G3">
-        <v>1998425.5</v>
+        <v>1997940.625</v>
       </c>
       <c r="H3">
-        <v>1.6618583686067719E-5</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -747,646 +728,646 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.504280805587769</v>
+        <v>2.959030866622925</v>
       </c>
       <c r="O3">
-        <v>2.4514884948730469</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="P3">
-        <v>1.4740914106369021</v>
+        <v>1.302545070648193</v>
       </c>
       <c r="Q3">
-        <v>0.77680391073226929</v>
+        <v>0.7281743288040161</v>
       </c>
       <c r="R3">
-        <v>0.47322705388069147</v>
+        <v>0.4705007672309875</v>
       </c>
       <c r="S3">
-        <v>0.39972203969955439</v>
+        <v>0.3997220396995544</v>
       </c>
       <c r="T3">
-        <v>0.56353223323822021</v>
+        <v>0.5161013603210449</v>
       </c>
       <c r="U3">
-        <v>0.52208280563354492</v>
+        <v>0.4860122203826904</v>
       </c>
       <c r="V3">
-        <v>0.47531557083129877</v>
+        <v>0.4609763622283936</v>
       </c>
       <c r="W3">
-        <v>0.44643580913543701</v>
+        <v>0.4362844228744507</v>
       </c>
       <c r="X3">
-        <v>0.4200412929058075</v>
+        <v>0.4146881997585297</v>
       </c>
       <c r="Y3">
-        <v>0.39982417225837708</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.3998241722583771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B4">
-        <v>2200686.75</v>
+        <v>2006591.375</v>
       </c>
       <c r="C4">
-        <v>2136481.5</v>
+        <v>2005085.625</v>
       </c>
       <c r="D4">
-        <v>2074556.5</v>
+        <v>2005066.125</v>
       </c>
       <c r="E4">
-        <v>2015104.375</v>
+        <v>2000683.25</v>
       </c>
       <c r="F4">
-        <v>2000199.875</v>
+        <v>2000014</v>
       </c>
       <c r="G4">
-        <v>1999736.25</v>
+        <v>1999444.5</v>
       </c>
       <c r="H4">
-        <v>3.549712181091309</v>
+        <v>2.240774631500244</v>
       </c>
       <c r="I4">
-        <v>2.269079208374023</v>
+        <v>1.129790306091309</v>
       </c>
       <c r="J4">
-        <v>1.417744398117065</v>
+        <v>0.5693498849868774</v>
       </c>
       <c r="K4">
-        <v>0.91735386848449707</v>
+        <v>0.368804931640625</v>
       </c>
       <c r="L4">
-        <v>0.57351326942443848</v>
+        <v>0.1834845542907715</v>
       </c>
       <c r="M4">
-        <v>0.40125322341918951</v>
+        <v>0.07219839096069336</v>
       </c>
       <c r="N4">
-        <v>15.642045974731451</v>
+        <v>12.83803749084473</v>
       </c>
       <c r="O4">
-        <v>10.45273590087891</v>
+        <v>8.686984062194824</v>
       </c>
       <c r="P4">
-        <v>5.3328180313110352</v>
+        <v>4.405914783477783</v>
       </c>
       <c r="Q4">
-        <v>1.357622504234314</v>
+        <v>1.189607977867126</v>
       </c>
       <c r="R4">
-        <v>0.23976659774780271</v>
+        <v>0.2253356277942657</v>
       </c>
       <c r="S4">
-        <v>4.3074972927570343E-3</v>
+        <v>0.004307497292757034</v>
       </c>
       <c r="T4">
-        <v>0.34816479682922358</v>
+        <v>0.3282365500926971</v>
       </c>
       <c r="U4">
-        <v>0.23428815603256231</v>
+        <v>0.2238170802593231</v>
       </c>
       <c r="V4">
-        <v>0.16966050863265991</v>
+        <v>0.1579315513372421</v>
       </c>
       <c r="W4">
-        <v>9.419095516204834E-2</v>
+        <v>0.0927807092666626</v>
       </c>
       <c r="X4">
-        <v>3.2848767936229713E-2</v>
+        <v>0.0328487828373909</v>
       </c>
       <c r="Y4">
-        <v>6.6018104553222656E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.006601810455322266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5">
-        <v>2036602.625</v>
+        <v>2000834.5</v>
       </c>
       <c r="C5">
-        <v>2024585.25</v>
+        <v>2000644.625</v>
       </c>
       <c r="D5">
-        <v>2013023.375</v>
+        <v>2000553.375</v>
       </c>
       <c r="E5">
-        <v>2002014.75</v>
+        <v>1998840.875</v>
       </c>
       <c r="F5">
-        <v>1999075.625</v>
+        <v>1997506.25</v>
       </c>
       <c r="G5">
-        <v>1998780.625</v>
+        <v>1997004.5</v>
       </c>
       <c r="H5">
-        <v>0.6632658839225769</v>
+        <v>0.3585156500339508</v>
       </c>
       <c r="I5">
-        <v>0.42830458283424377</v>
+        <v>0.2183156460523605</v>
       </c>
       <c r="J5">
-        <v>0.28444328904151922</v>
+        <v>0.1059751212596893</v>
       </c>
       <c r="K5">
-        <v>0.18893107771873471</v>
+        <v>0.05546875298023224</v>
       </c>
       <c r="L5">
-        <v>0.11713364720344541</v>
+        <v>0.02180173248052597</v>
       </c>
       <c r="M5">
-        <v>6.6136762499809265E-2</v>
+        <v>0.00583988893777132</v>
       </c>
       <c r="N5">
-        <v>1.8550188541412349</v>
+        <v>1.261049509048462</v>
       </c>
       <c r="O5">
-        <v>1.095117568969727</v>
+        <v>0.7659054398536682</v>
       </c>
       <c r="P5">
-        <v>0.40080001950263983</v>
+        <v>0.2947682738304138</v>
       </c>
       <c r="Q5">
-        <v>6.5314017236232758E-2</v>
+        <v>0.05730795487761497</v>
       </c>
       <c r="R5">
-        <v>1.0391665622591971E-2</v>
+        <v>0.009923342615365982</v>
       </c>
       <c r="S5">
-        <v>1.29651089082472E-4</v>
+        <v>0.000129651089082472</v>
       </c>
       <c r="T5">
-        <v>2.415052987635136E-2</v>
+        <v>0.02150707505643368</v>
       </c>
       <c r="U5">
-        <v>1.600881852209568E-2</v>
+        <v>0.01405694615095854</v>
       </c>
       <c r="V5">
-        <v>1.028259098529816E-2</v>
+        <v>0.008854876272380352</v>
       </c>
       <c r="W5">
-        <v>5.1611959934234619E-3</v>
+        <v>0.005062696523964405</v>
       </c>
       <c r="X5">
-        <v>2.129776636138558E-3</v>
+        <v>0.002102917060256004</v>
       </c>
       <c r="Y5">
-        <v>1.3436230074148631E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+        <v>0.0001343623007414863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3">
-        <v>2203375</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2139052.25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2076991.25</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2017952</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2000301.625</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1999736.25</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3.549712181091309</v>
-      </c>
-      <c r="I6" s="3">
-        <v>2.269079208374023</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1.417744398117065</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.91735386848449707</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.57351326942443848</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.40125322341918951</v>
-      </c>
-      <c r="N6" s="3">
-        <v>30.882781982421879</v>
-      </c>
-      <c r="O6" s="3">
-        <v>22.908357620239261</v>
-      </c>
-      <c r="P6" s="3">
-        <v>15.28395938873291</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>9.9349193572998047</v>
-      </c>
-      <c r="R6" s="3">
-        <v>7.1496262550354004</v>
-      </c>
-      <c r="S6" s="3">
-        <v>6.3218646049499512</v>
-      </c>
-      <c r="T6" s="3">
-        <v>7.6940097808837891</v>
-      </c>
-      <c r="U6" s="3">
-        <v>7.2213387489318848</v>
-      </c>
-      <c r="V6" s="3">
-        <v>6.9422745704650879</v>
-      </c>
-      <c r="W6" s="3">
-        <v>6.6859946250915527</v>
-      </c>
-      <c r="X6" s="3">
-        <v>6.4577927589416504</v>
-      </c>
-      <c r="Y6" s="3">
+      <c r="B6">
+        <v>2027047.875</v>
+      </c>
+      <c r="C6">
+        <v>2019291</v>
+      </c>
+      <c r="D6">
+        <v>2011222.625</v>
+      </c>
+      <c r="E6">
+        <v>2000683.25</v>
+      </c>
+      <c r="F6">
+        <v>2000014</v>
+      </c>
+      <c r="G6">
+        <v>1999470.875</v>
+      </c>
+      <c r="H6">
+        <v>2.240774631500244</v>
+      </c>
+      <c r="I6">
+        <v>1.129790306091309</v>
+      </c>
+      <c r="J6">
+        <v>0.5693498849868774</v>
+      </c>
+      <c r="K6">
+        <v>0.368804931640625</v>
+      </c>
+      <c r="L6">
+        <v>0.1834845542907715</v>
+      </c>
+      <c r="M6">
+        <v>0.07219839096069336</v>
+      </c>
+      <c r="N6">
+        <v>26.44383239746094</v>
+      </c>
+      <c r="O6">
+        <v>20.32553100585938</v>
+      </c>
+      <c r="P6">
+        <v>14.35314750671387</v>
+      </c>
+      <c r="Q6">
+        <v>9.646162986755371</v>
+      </c>
+      <c r="R6">
+        <v>7.103845596313477</v>
+      </c>
+      <c r="S6">
+        <v>6.321864604949951</v>
+      </c>
+      <c r="T6">
+        <v>7.489950656890869</v>
+      </c>
+      <c r="U6">
+        <v>7.185243129730225</v>
+      </c>
+      <c r="V6">
+        <v>6.933363437652588</v>
+      </c>
+      <c r="W6">
+        <v>6.681993007659912</v>
+      </c>
+      <c r="X6">
+        <v>6.456469058990479</v>
+      </c>
+      <c r="Y6">
         <v>6.302091121673584</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B7">
-        <v>2035961.75</v>
+        <v>2002270.25</v>
       </c>
       <c r="C7">
-        <v>2024056.5</v>
+        <v>2002126.25</v>
       </c>
       <c r="D7">
-        <v>2012597.75</v>
+        <v>2001304.5</v>
       </c>
       <c r="E7">
-        <v>2001749.125</v>
+        <v>1999114</v>
       </c>
       <c r="F7">
-        <v>1998901.75</v>
+        <v>1997964.25</v>
       </c>
       <c r="G7">
-        <v>1998603.125</v>
+        <v>1997472.625</v>
       </c>
       <c r="H7">
-        <v>0.33164125680923462</v>
+        <v>0.1792578250169754</v>
       </c>
       <c r="I7">
-        <v>0.21415230631828311</v>
+        <v>0.1091578230261803</v>
       </c>
       <c r="J7">
-        <v>0.14222164452075961</v>
+        <v>0.05298756062984467</v>
       </c>
       <c r="K7">
-        <v>9.4465538859367371E-2</v>
+        <v>0.02773437649011612</v>
       </c>
       <c r="L7">
-        <v>5.8566823601722717E-2</v>
+        <v>0.01090086624026299</v>
       </c>
       <c r="M7">
-        <v>3.3068381249904633E-2</v>
+        <v>0.00291994446888566</v>
       </c>
       <c r="N7">
-        <v>3.417477130889893</v>
+        <v>2.86966347694397</v>
       </c>
       <c r="O7">
-        <v>2.3801004886627202</v>
+        <v>2.036016702651978</v>
       </c>
       <c r="P7">
-        <v>1.41760241985321</v>
+        <v>1.249504446983337</v>
       </c>
       <c r="Q7">
-        <v>0.73935705423355103</v>
+        <v>0.6928654909133911</v>
       </c>
       <c r="R7">
-        <v>0.4488673210144043</v>
+        <v>0.4462598860263824</v>
       </c>
       <c r="S7">
-        <v>0.37869086861610413</v>
+        <v>0.3786908686161041</v>
       </c>
       <c r="T7">
-        <v>0.53514373302459717</v>
+        <v>0.4900700747966766</v>
       </c>
       <c r="U7">
-        <v>0.49544736742973328</v>
+        <v>0.461172491312027</v>
       </c>
       <c r="V7">
-        <v>0.45084014534950262</v>
+        <v>0.4371805191040039</v>
       </c>
       <c r="W7">
-        <v>0.42321079969406128</v>
+        <v>0.4135885238647461</v>
       </c>
       <c r="X7">
-        <v>0.39804598689079279</v>
+        <v>0.3929731845855713</v>
       </c>
       <c r="Y7">
-        <v>0.37878784537315369</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.3787878453731537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B8">
-        <v>238975.4375</v>
+        <v>30613.466796875</v>
       </c>
       <c r="C8">
-        <v>163141.4375</v>
+        <v>21389.287109375</v>
       </c>
       <c r="D8">
-        <v>90434.71875</v>
+        <v>10516.646484375</v>
       </c>
       <c r="E8">
-        <v>19232.828125</v>
+        <v>3561.450439453125</v>
       </c>
       <c r="F8">
-        <v>2049.689453125</v>
+        <v>1525.439331054688</v>
       </c>
       <c r="G8">
-        <v>1264.296508789062</v>
+        <v>1248.453491210938</v>
       </c>
       <c r="H8">
-        <v>2.1585693359375</v>
+        <v>1.041920065879822</v>
       </c>
       <c r="I8">
-        <v>1.128277182579041</v>
+        <v>0.7028317451477051</v>
       </c>
       <c r="J8">
-        <v>0.78890180587768555</v>
+        <v>0.4562695920467377</v>
       </c>
       <c r="K8">
-        <v>0.58284938335418701</v>
+        <v>0.2568489611148834</v>
       </c>
       <c r="L8">
-        <v>0.42568942904472351</v>
+        <v>0.06742724776268005</v>
       </c>
       <c r="M8">
-        <v>0.28922587633132929</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>44320.12890625</v>
+        <v>8545.890625</v>
       </c>
       <c r="C9">
-        <v>30235.34375</v>
+        <v>6404.98095703125</v>
       </c>
       <c r="D9">
-        <v>16977.154296875</v>
+        <v>3733.2705078125</v>
       </c>
       <c r="E9">
-        <v>4158.78271484375</v>
+        <v>1232.762573242188</v>
       </c>
       <c r="F9">
-        <v>905.30889892578125</v>
+        <v>550.6669921875</v>
       </c>
       <c r="G9">
-        <v>657.7825927734375</v>
+        <v>370.5406188964844</v>
       </c>
       <c r="H9">
-        <v>0.36435306072235107</v>
+        <v>0.1759846806526184</v>
       </c>
       <c r="I9">
-        <v>0.16651557385921481</v>
+        <v>0.0941707119345665</v>
       </c>
       <c r="J9">
-        <v>9.4700105488300323E-2</v>
+        <v>0.04323341324925423</v>
       </c>
       <c r="K9">
-        <v>5.8164384216070182E-2</v>
+        <v>0.01435147598385811</v>
       </c>
       <c r="L9">
-        <v>3.7098824977874763E-2</v>
+        <v>0.003745958209037781</v>
       </c>
       <c r="M9">
-        <v>2.2657284513115879E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B10">
-        <v>241116.359375</v>
+        <v>23989.03125</v>
       </c>
       <c r="C10">
-        <v>165058.9375</v>
+        <v>21704.357421875</v>
       </c>
       <c r="D10">
-        <v>92111.8828125</v>
+        <v>9455.61328125</v>
       </c>
       <c r="E10">
-        <v>20444.427734375</v>
+        <v>3136.26318359375</v>
       </c>
       <c r="F10">
-        <v>2100.323486328125</v>
+        <v>1844.8310546875</v>
       </c>
       <c r="G10">
-        <v>1475.618408203125</v>
+        <v>1474.5615234375</v>
       </c>
       <c r="H10">
-        <v>2.272098064422607</v>
+        <v>1.605820655822754</v>
       </c>
       <c r="I10">
-        <v>1.532704830169678</v>
+        <v>1.155309438705444</v>
       </c>
       <c r="J10">
-        <v>0.92079877853393555</v>
+        <v>0.7466700077056885</v>
       </c>
       <c r="K10">
-        <v>0.47173881530761719</v>
+        <v>0.3688483238220215</v>
       </c>
       <c r="L10">
         <v>0.1429440975189209</v>
       </c>
       <c r="M10">
-        <v>3.9496183395385742E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.03949618339538574</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B11">
-        <v>44983.60546875</v>
+        <v>8372.7470703125</v>
       </c>
       <c r="C11">
-        <v>30698.96484375</v>
+        <v>6819.97314453125</v>
       </c>
       <c r="D11">
-        <v>17326.2421875</v>
+        <v>3530.60205078125</v>
       </c>
       <c r="E11">
-        <v>4444.658203125</v>
+        <v>1352.830078125</v>
       </c>
       <c r="F11">
-        <v>1024.867431640625</v>
+        <v>688.0409545898438</v>
       </c>
       <c r="G11">
-        <v>728.0872802734375</v>
+        <v>499.1234130859375</v>
       </c>
       <c r="H11">
-        <v>0.17099560797214511</v>
+        <v>0.2992283403873444</v>
       </c>
       <c r="I11">
-        <v>7.7653795480728149E-2</v>
+        <v>0.1941424459218979</v>
       </c>
       <c r="J11">
-        <v>3.741774708032608E-2</v>
+        <v>0.1168851032853127</v>
       </c>
       <c r="K11">
-        <v>1.50759257376194E-2</v>
+        <v>0.04881447181105614</v>
       </c>
       <c r="L11">
-        <v>3.0085362959653139E-3</v>
+        <v>0.009724259376525879</v>
       </c>
       <c r="M11">
-        <v>3.9989160723052919E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+        <v>0.002194232307374477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3">
-        <v>241116.359375</v>
-      </c>
-      <c r="C12" s="3">
-        <v>165058.9375</v>
-      </c>
-      <c r="D12" s="3">
-        <v>92111.8828125</v>
-      </c>
-      <c r="E12" s="3">
-        <v>20444.427734375</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2100.323486328125</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1475.618408203125</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2.272098064422607</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1.532704830169678</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.92079877853393555</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0.58284938335418701</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0.42568942904472351</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0.28922587633132929</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>30613.466796875</v>
+      </c>
+      <c r="C12">
+        <v>21704.357421875</v>
+      </c>
+      <c r="D12">
+        <v>10516.646484375</v>
+      </c>
+      <c r="E12">
+        <v>3561.450439453125</v>
+      </c>
+      <c r="F12">
+        <v>1844.8310546875</v>
+      </c>
+      <c r="G12">
+        <v>1474.5615234375</v>
+      </c>
+      <c r="H12">
+        <v>1.605820655822754</v>
+      </c>
+      <c r="I12">
+        <v>1.155309438705444</v>
+      </c>
+      <c r="J12">
+        <v>0.7466700077056885</v>
+      </c>
+      <c r="K12">
+        <v>0.3688483238220215</v>
+      </c>
+      <c r="L12">
+        <v>0.1429440975189209</v>
+      </c>
+      <c r="M12">
+        <v>0.03949618339538574</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B13">
-        <v>44651.859375</v>
+        <v>8459.318359375</v>
       </c>
       <c r="C13">
-        <v>30467.15234375</v>
+        <v>6612.47705078125</v>
       </c>
       <c r="D13">
-        <v>17151.697265625</v>
+        <v>3631.936279296875</v>
       </c>
       <c r="E13">
-        <v>4301.72021484375</v>
+        <v>1292.79638671875</v>
       </c>
       <c r="F13">
-        <v>965.088134765625</v>
+        <v>619.3539428710938</v>
       </c>
       <c r="G13">
-        <v>692.9349365234375</v>
+        <v>434.83203125</v>
       </c>
       <c r="H13">
-        <v>0.26767432689666748</v>
+        <v>0.2376065254211426</v>
       </c>
       <c r="I13">
-        <v>0.12208468466997149</v>
+        <v>0.1441565752029419</v>
       </c>
       <c r="J13">
-        <v>6.6058926284313202E-2</v>
+        <v>0.08005926012992859</v>
       </c>
       <c r="K13">
-        <v>3.6620154976844788E-2</v>
+        <v>0.03158297389745712</v>
       </c>
       <c r="L13">
-        <v>2.0053679123520851E-2</v>
+        <v>0.00673510879278183</v>
       </c>
       <c r="M13">
-        <v>1.152858790010214E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+        <v>0.001097116153687239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3">
-        <v>194.39076232910159</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14">
+        <v>194.3907623291016</v>
+      </c>
+      <c r="C14">
         <v>133.3813171386719</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>77.05206298828125</v>
       </c>
-      <c r="E14" s="3">
-        <v>18.514150619506839</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14">
+        <v>18.51415061950684</v>
+      </c>
+      <c r="F14">
         <v>0.7961125373840332</v>
       </c>
-      <c r="G14" s="3">
-        <v>2.1535396575927731E-2</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14">
+        <v>0.02153539657592773</v>
+      </c>
+      <c r="H14">
         <v>1.023346900939941</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14">
         <v>0.3577582836151123</v>
       </c>
-      <c r="J14" s="3">
-        <v>3.4685134887695313E-2</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1.7433047294616699E-2</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3.4728050231933589E-3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <v>0.03468513488769531</v>
+      </c>
+      <c r="K14">
+        <v>0.0174330472946167</v>
+      </c>
+      <c r="L14">
+        <v>0.003472805023193359</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B15">
-        <v>17.974262237548832</v>
+        <v>17.97426223754883</v>
       </c>
       <c r="C15">
-        <v>11.693166732788089</v>
+        <v>11.69316673278809</v>
       </c>
       <c r="D15">
         <v>5.874701976776123</v>
@@ -1395,572 +1376,818 @@
         <v>0.7902531623840332</v>
       </c>
       <c r="F15">
-        <v>5.1300288178026676E-3</v>
+        <v>0.005130028817802668</v>
       </c>
       <c r="G15">
-        <v>8.3119637565687299E-5</v>
+        <v>8.31196375656873E-05</v>
       </c>
       <c r="H15">
-        <v>1.5951827168464661E-2</v>
+        <v>0.01595182716846466</v>
       </c>
       <c r="I15">
-        <v>2.6392708532512188E-3</v>
+        <v>0.002639270853251219</v>
       </c>
       <c r="J15">
-        <v>2.05983393243514E-4</v>
+        <v>0.000205983393243514</v>
       </c>
       <c r="K15">
-        <v>6.1434766394086182E-5</v>
+        <v>6.143476639408618E-05</v>
       </c>
       <c r="L15">
-        <v>9.3354974524118006E-6</v>
+        <v>9.335497452411801E-06</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B16">
-        <v>3.0802149772644039</v>
+        <v>3.080214977264404</v>
       </c>
       <c r="C16">
-        <v>2.2170982360839839</v>
+        <v>2.217098236083984</v>
       </c>
       <c r="D16">
-        <v>1.4167995452880859</v>
+        <v>1.416799545288086</v>
       </c>
       <c r="E16">
-        <v>0.25152742862701422</v>
+        <v>0.2515274286270142</v>
       </c>
       <c r="F16">
-        <v>8.5074424743652344E-2</v>
+        <v>0.08507442474365234</v>
       </c>
       <c r="G16">
-        <v>7.0321202278137207E-2</v>
+        <v>0.07032120227813721</v>
       </c>
       <c r="H16">
         <v>0.1158580780029297</v>
       </c>
       <c r="I16">
-        <v>8.4692716598510742E-2</v>
+        <v>0.08469271659851074</v>
       </c>
       <c r="J16">
-        <v>6.654059886932373E-2</v>
+        <v>0.06654059886932373</v>
       </c>
       <c r="K16">
-        <v>5.9296727180480957E-2</v>
+        <v>0.05929672718048096</v>
       </c>
       <c r="L16">
-        <v>5.2530646324157708E-2</v>
+        <v>0.05253064632415771</v>
       </c>
       <c r="M16">
-        <v>4.8322200775146477E-2</v>
-      </c>
-      <c r="N16">
-        <v>0.52029573917388916</v>
-      </c>
-      <c r="O16">
-        <v>0.35599029064178472</v>
-      </c>
-      <c r="P16">
-        <v>0.1942821741104126</v>
-      </c>
-      <c r="Q16">
-        <v>7.1271181106567383E-2</v>
-      </c>
-      <c r="R16">
-        <v>1.5257716178894039E-2</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>3.0920743942260739E-2</v>
-      </c>
-      <c r="U16">
-        <v>2.2446870803833011E-2</v>
-      </c>
-      <c r="V16">
-        <v>1.558482646942139E-2</v>
-      </c>
-      <c r="W16">
-        <v>9.0999603271484375E-3</v>
-      </c>
-      <c r="X16">
-        <v>3.3349990844726558E-3</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.04832220077514648</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B17">
-        <v>0.59723305702209473</v>
+        <v>0.5972330570220947</v>
       </c>
       <c r="C17">
-        <v>0.45392432808876038</v>
+        <v>0.4539243280887604</v>
       </c>
       <c r="D17">
-        <v>0.23310837149620059</v>
+        <v>0.2331083714962006</v>
       </c>
       <c r="E17">
-        <v>8.6625166237354279E-2</v>
+        <v>0.08662516623735428</v>
       </c>
       <c r="F17">
-        <v>4.3894559144973748E-2</v>
+        <v>0.04389455914497375</v>
       </c>
       <c r="G17">
-        <v>2.4523157626390461E-2</v>
+        <v>0.02452315762639046</v>
       </c>
       <c r="H17">
-        <v>6.1988577246665948E-2</v>
+        <v>0.06198857724666595</v>
       </c>
       <c r="I17">
-        <v>4.6126898378133767E-2</v>
+        <v>0.04612689837813377</v>
       </c>
       <c r="J17">
-        <v>3.639129176735878E-2</v>
+        <v>0.03639129176735878</v>
       </c>
       <c r="K17">
-        <v>2.760391682386398E-2</v>
+        <v>0.02760391682386398</v>
       </c>
       <c r="L17">
-        <v>1.984345726668835E-2</v>
+        <v>0.01984345726668835</v>
       </c>
       <c r="M17">
-        <v>1.461991108953953E-2</v>
-      </c>
-      <c r="N17">
-        <v>0.44643530249595642</v>
-      </c>
-      <c r="O17">
-        <v>0.30079621076583862</v>
-      </c>
-      <c r="P17">
-        <v>0.15971930325031281</v>
-      </c>
-      <c r="Q17">
-        <v>4.9821767956018448E-2</v>
-      </c>
-      <c r="R17">
-        <v>4.1119391098618507E-3</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>1.2118173763155941E-2</v>
-      </c>
-      <c r="U17">
-        <v>6.5347086638212204E-3</v>
-      </c>
-      <c r="V17">
-        <v>3.2160347327589989E-3</v>
-      </c>
-      <c r="W17">
-        <v>1.360224327072501E-3</v>
-      </c>
-      <c r="X17">
-        <v>3.3429596805945039E-4</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.01461991108953953</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B18">
-        <v>2.072689294815063</v>
+        <v>0.8983200788497925</v>
       </c>
       <c r="C18">
-        <v>1.2585973739624019</v>
+        <v>0.7605264186859131</v>
       </c>
       <c r="D18">
-        <v>0.57984626293182373</v>
+        <v>0.5931743383407593</v>
       </c>
       <c r="E18">
-        <v>0.31627815961837769</v>
+        <v>0.1227995157241821</v>
       </c>
       <c r="F18">
-        <v>9.5214545726776123E-2</v>
+        <v>0.08507442474365234</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.07032120227813721</v>
       </c>
       <c r="H18">
-        <v>0.32168692350387568</v>
+        <v>0.1158580780029297</v>
       </c>
       <c r="I18">
-        <v>0.22672766447067261</v>
+        <v>0.08469271659851074</v>
       </c>
       <c r="J18">
-        <v>0.13832575082778931</v>
+        <v>0.06654059886932373</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>0.05929672718048096</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.05253064632415771</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>0.04832220077514648</v>
       </c>
       <c r="N18">
-        <v>0.29677325487136841</v>
+        <v>0.4485063552856445</v>
       </c>
       <c r="O18">
-        <v>0.17149823904037481</v>
+        <v>0.309362530708313</v>
       </c>
       <c r="P18">
-        <v>5.5734634399414063E-2</v>
+        <v>0.1717597246170044</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>0.06618285179138184</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.01502060890197754</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.02912092208862305</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>0.02159059047698975</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>0.01523661613464355</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>0.008941054344177246</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>0.003296375274658203</v>
       </c>
       <c r="Y18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <v>0.61661595106124878</v>
+        <v>0.5263351202011108</v>
       </c>
       <c r="C19">
-        <v>0.48364433646202087</v>
+        <v>0.3798178434371948</v>
       </c>
       <c r="D19">
-        <v>0.31427007913589478</v>
+        <v>0.2074008733034134</v>
       </c>
       <c r="E19">
-        <v>0.1006647422909737</v>
+        <v>0.09394946694374084</v>
       </c>
       <c r="F19">
-        <v>2.3461722303181891E-3</v>
+        <v>0.05090417340397835</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.02869928628206253</v>
       </c>
       <c r="H19">
-        <v>6.9195643067359924E-2</v>
+        <v>0.06882882118225098</v>
       </c>
       <c r="I19">
-        <v>9.1597065329551697E-3</v>
+        <v>0.05352978408336639</v>
       </c>
       <c r="J19">
-        <v>4.4395942240953454E-3</v>
+        <v>0.04196493327617645</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>0.03105433098971844</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>0.02121143229305744</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>0.01580048352479935</v>
       </c>
       <c r="N19">
-        <v>0.15978573262691501</v>
+        <v>0.3850928246974945</v>
       </c>
       <c r="O19">
-        <v>7.8402914106845856E-2</v>
+        <v>0.2615264356136322</v>
       </c>
       <c r="P19">
-        <v>6.9102579727768898E-3</v>
+        <v>0.1395338922739029</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>0.04482899233698845</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>0.003921740688383579</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.01057482417672873</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>0.005818764213472605</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>0.003013663925230503</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>0.001330097555182874</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>0.0003272030153311789</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:25">
+      <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3">
-        <v>3.0802149772644039</v>
-      </c>
-      <c r="C20" s="3">
-        <v>2.2170982360839839</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1.4167995452880859</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.31627815961837769</v>
-      </c>
-      <c r="F20" s="3">
-        <v>9.5214545726776123E-2</v>
-      </c>
-      <c r="G20" s="3">
-        <v>7.0321202278137207E-2</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.32168692350387568</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0.22672766447067261</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0.13832575082778931</v>
-      </c>
-      <c r="K20" s="3">
-        <v>5.9296727180480957E-2</v>
-      </c>
-      <c r="L20" s="3">
-        <v>5.2530646324157708E-2</v>
-      </c>
-      <c r="M20" s="3">
-        <v>4.8322200775146477E-2</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0.52029573917388916</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0.35599029064178472</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0.1942821741104126</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>7.1271181106567383E-2</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1.5257716178894039E-2</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3.0920743942260739E-2</v>
-      </c>
-      <c r="U20" s="3">
-        <v>2.2446870803833011E-2</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1.558482646942139E-2</v>
-      </c>
-      <c r="W20" s="3">
-        <v>9.0999603271484375E-3</v>
-      </c>
-      <c r="X20" s="3">
-        <v>3.3349990844726558E-3</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>2.072689294815063</v>
+      </c>
+      <c r="C20">
+        <v>1.258597373962402</v>
+      </c>
+      <c r="D20">
+        <v>0.5798462629318237</v>
+      </c>
+      <c r="E20">
+        <v>0.3162781596183777</v>
+      </c>
+      <c r="F20">
+        <v>0.09521454572677612</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.3216869235038757</v>
+      </c>
+      <c r="I20">
+        <v>0.2267276644706726</v>
+      </c>
+      <c r="J20">
+        <v>0.1383257508277893</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B21">
-        <v>0.60692447423934937</v>
+        <v>0.6166159510612488</v>
       </c>
       <c r="C21">
-        <v>0.4687843918800354</v>
+        <v>0.4836443364620209</v>
       </c>
       <c r="D21">
-        <v>0.27368924021720892</v>
+        <v>0.3142700791358948</v>
       </c>
       <c r="E21">
-        <v>9.3644961714744568E-2</v>
+        <v>0.1006647422909737</v>
       </c>
       <c r="F21">
-        <v>2.3120366036891941E-2</v>
+        <v>0.002346172230318189</v>
       </c>
       <c r="G21">
-        <v>1.226157881319523E-2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>6.5592110157012939E-2</v>
+        <v>0.06919564306735992</v>
       </c>
       <c r="I21">
-        <v>2.7643304318189621E-2</v>
+        <v>0.00915970653295517</v>
       </c>
       <c r="J21">
-        <v>2.041544392704964E-2</v>
+        <v>0.004439594224095345</v>
       </c>
       <c r="K21">
-        <v>1.380195841193199E-2</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>9.9217286333441734E-3</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>7.3099555447697639E-3</v>
-      </c>
-      <c r="N21">
-        <v>0.30311048030853271</v>
-      </c>
-      <c r="O21">
-        <v>0.18959957361221311</v>
-      </c>
-      <c r="P21">
-        <v>8.3314791321754456E-2</v>
-      </c>
-      <c r="Q21">
-        <v>2.491088397800922E-2</v>
-      </c>
-      <c r="R21">
-        <v>2.0559695549309249E-3</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>6.0590868815779686E-3</v>
-      </c>
-      <c r="U21">
-        <v>3.2673543319106102E-3</v>
-      </c>
-      <c r="V21">
-        <v>1.608017366379499E-3</v>
-      </c>
-      <c r="W21">
-        <v>6.8011216353625059E-4</v>
-      </c>
-      <c r="X21">
-        <v>1.6714798402972519E-4</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="3">
-        <v>1.6212319135665889</v>
-      </c>
-      <c r="C22" s="3">
-        <v>1.509797215461731</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1.415184020996094</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1.3461416959762571</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1.3122044801712041</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1.2972608804702761</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1.3278907537460329</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1.314678311347961</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1.3040504455566411</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1.2956333160400391</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1.28966236114502</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1.2863351106643679</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>0.9433035254478455</v>
+      </c>
+      <c r="C22">
+        <v>0.7890971302986145</v>
+      </c>
+      <c r="D22">
+        <v>0.5798462629318237</v>
+      </c>
+      <c r="E22">
+        <v>0.2664653658866882</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0.3029770255088806</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0.1796738505363464</v>
+      </c>
+      <c r="O22">
+        <v>0.1024823188781738</v>
+      </c>
+      <c r="P22">
+        <v>0.02039819955825806</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B23">
-        <v>1.0913040637969971</v>
+        <v>0.6371212601661682</v>
       </c>
       <c r="C23">
-        <v>0.99887967109680176</v>
+        <v>0.5147944092750549</v>
       </c>
       <c r="D23">
-        <v>0.93229758739471436</v>
+        <v>0.3433551490306854</v>
       </c>
       <c r="E23">
-        <v>0.89350271224975586</v>
+        <v>0.05014454200863838</v>
       </c>
       <c r="F23">
-        <v>0.88003867864608765</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0.87460958957672119</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0.88421922922134399</v>
+        <v>0.04835681617259979</v>
       </c>
       <c r="I23">
-        <v>0.88059824705123901</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.87772142887115479</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0.87542879581451416</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>0.87367957830429077</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>0.87268322706222534</v>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0.09067833423614502</v>
+      </c>
+      <c r="O23">
+        <v>0.04193269088864326</v>
+      </c>
+      <c r="P23">
+        <v>0.001199811697006226</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>3.080214977264404</v>
+      </c>
+      <c r="C24">
+        <v>2.217098236083984</v>
+      </c>
+      <c r="D24">
+        <v>1.416799545288086</v>
+      </c>
+      <c r="E24">
+        <v>0.3162781596183777</v>
+      </c>
+      <c r="F24">
+        <v>0.09521454572677612</v>
+      </c>
+      <c r="G24">
+        <v>0.07032120227813721</v>
+      </c>
+      <c r="H24">
+        <v>0.3216869235038757</v>
+      </c>
+      <c r="I24">
+        <v>0.2267276644706726</v>
+      </c>
+      <c r="J24">
+        <v>0.1383257508277893</v>
+      </c>
+      <c r="K24">
+        <v>0.05929672718048096</v>
+      </c>
+      <c r="L24">
+        <v>0.05253064632415771</v>
+      </c>
+      <c r="M24">
+        <v>0.04832220077514648</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>0.6069244742393494</v>
+      </c>
+      <c r="C25">
+        <v>0.4687843918800354</v>
+      </c>
+      <c r="D25">
+        <v>0.2736892402172089</v>
+      </c>
+      <c r="E25">
+        <v>0.09364496171474457</v>
+      </c>
+      <c r="F25">
+        <v>0.02312036603689194</v>
+      </c>
+      <c r="G25">
+        <v>0.01226157881319523</v>
+      </c>
+      <c r="H25">
+        <v>0.06559211015701294</v>
+      </c>
+      <c r="I25">
+        <v>0.02764330431818962</v>
+      </c>
+      <c r="J25">
+        <v>0.02041544392704964</v>
+      </c>
+      <c r="K25">
+        <v>0.01380195841193199</v>
+      </c>
+      <c r="L25">
+        <v>0.009921728633344173</v>
+      </c>
+      <c r="M25">
+        <v>0.007309955544769764</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>0.9433035254478455</v>
+      </c>
+      <c r="C26">
+        <v>0.7890971302986145</v>
+      </c>
+      <c r="D26">
+        <v>0.5931743383407593</v>
+      </c>
+      <c r="E26">
+        <v>0.2664653658866882</v>
+      </c>
+      <c r="F26">
+        <v>0.08507442474365234</v>
+      </c>
+      <c r="G26">
+        <v>0.07032120227813721</v>
+      </c>
+      <c r="H26">
+        <v>0.3029770255088806</v>
+      </c>
+      <c r="I26">
+        <v>0.08469271659851074</v>
+      </c>
+      <c r="J26">
+        <v>0.06654059886932373</v>
+      </c>
+      <c r="K26">
+        <v>0.05929672718048096</v>
+      </c>
+      <c r="L26">
+        <v>0.05253064632415771</v>
+      </c>
+      <c r="M26">
+        <v>0.04832220077514648</v>
+      </c>
+      <c r="N26">
+        <v>0.4485063552856445</v>
+      </c>
+      <c r="O26">
+        <v>0.309362530708313</v>
+      </c>
+      <c r="P26">
+        <v>0.1717597246170044</v>
+      </c>
+      <c r="Q26">
+        <v>0.06618285179138184</v>
+      </c>
+      <c r="R26">
+        <v>0.01502060890197754</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0.02912092208862305</v>
+      </c>
+      <c r="U26">
+        <v>0.02159059047698975</v>
+      </c>
+      <c r="V26">
+        <v>0.01523661613464355</v>
+      </c>
+      <c r="W26">
+        <v>0.008941054344177246</v>
+      </c>
+      <c r="X26">
+        <v>0.003296375274658203</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>0.5817282199859619</v>
+      </c>
+      <c r="C27">
+        <v>0.447306215763092</v>
+      </c>
+      <c r="D27">
+        <v>0.2753779888153076</v>
+      </c>
+      <c r="E27">
+        <v>0.07204701006412506</v>
+      </c>
+      <c r="F27">
+        <v>0.02545208670198917</v>
+      </c>
+      <c r="G27">
+        <v>0.01434964314103127</v>
+      </c>
+      <c r="H27">
+        <v>0.05859282240271568</v>
+      </c>
+      <c r="I27">
+        <v>0.0267648920416832</v>
+      </c>
+      <c r="J27">
+        <v>0.02098246663808823</v>
+      </c>
+      <c r="K27">
+        <v>0.01552716549485922</v>
+      </c>
+      <c r="L27">
+        <v>0.01060571614652872</v>
+      </c>
+      <c r="M27">
+        <v>0.007900241762399673</v>
+      </c>
+      <c r="N27">
+        <v>0.2378855794668198</v>
+      </c>
+      <c r="O27">
+        <v>0.1517295688390732</v>
+      </c>
+      <c r="P27">
+        <v>0.07036685198545456</v>
+      </c>
+      <c r="Q27">
+        <v>0.02241449616849422</v>
+      </c>
+      <c r="R27">
+        <v>0.00196087034419179</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0.005287412088364363</v>
+      </c>
+      <c r="U27">
+        <v>0.002909382106736302</v>
+      </c>
+      <c r="V27">
+        <v>0.001506831962615252</v>
+      </c>
+      <c r="W27">
+        <v>0.0006650487775914371</v>
+      </c>
+      <c r="X27">
+        <v>0.0001636015076655895</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>1.539815306663513</v>
+      </c>
+      <c r="C28">
+        <v>1.455911040306091</v>
+      </c>
+      <c r="D28">
+        <v>1.386166095733643</v>
+      </c>
+      <c r="E28">
+        <v>1.337505340576172</v>
+      </c>
+      <c r="F28">
+        <v>1.31172239780426</v>
+      </c>
+      <c r="G28">
+        <v>1.297229766845703</v>
+      </c>
+      <c r="H28">
+        <v>1.326926231384277</v>
+      </c>
+      <c r="I28">
+        <v>1.314356446266174</v>
+      </c>
+      <c r="J28">
+        <v>1.304000020027161</v>
+      </c>
+      <c r="K28">
+        <v>1.295633316040039</v>
+      </c>
+      <c r="L28">
+        <v>1.28966236114502</v>
+      </c>
+      <c r="M28">
+        <v>1.286335110664368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>0.9939618706703186</v>
+      </c>
+      <c r="C29">
+        <v>0.9515977501869202</v>
+      </c>
+      <c r="D29">
+        <v>0.9159565567970276</v>
+      </c>
+      <c r="E29">
+        <v>0.8905561566352844</v>
+      </c>
+      <c r="F29">
+        <v>0.8797488808631897</v>
+      </c>
+      <c r="G29">
+        <v>0.8745918273925781</v>
+      </c>
+      <c r="H29">
+        <v>0.8836096525192261</v>
+      </c>
+      <c r="I29">
+        <v>0.8804020881652832</v>
+      </c>
+      <c r="J29">
+        <v>0.8776777386665344</v>
+      </c>
+      <c r="K29">
+        <v>0.8754273653030396</v>
+      </c>
+      <c r="L29">
+        <v>0.8736795783042908</v>
+      </c>
+      <c r="M29">
+        <v>0.8726832270622253</v>
       </c>
     </row>
   </sheetData>

--- a/verification/model_verification_results_118_buses_raw.xlsx
+++ b/verification/model_verification_results_118_buses_raw.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\verification\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E014DF42-2B63-4306-BFD9-9AD29F0F05D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -178,8 +184,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,12 +202,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -231,24 +243,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -286,7 +310,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -320,6 +344,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -354,9 +379,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,11 +555,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -610,27 +639,27 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B2">
-        <v>2027047.875</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2019291</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>2011222.625</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2000436.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1999940.75</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1999470.875</v>
+        <v>3.5447597503662109E-2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -651,63 +680,63 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>26.44383239746094</v>
+        <v>21.238359451293949</v>
       </c>
       <c r="O2">
-        <v>20.32553100585938</v>
+        <v>14.7111873626709</v>
       </c>
       <c r="P2">
-        <v>14.35314750671387</v>
+        <v>8.3353328704833984</v>
       </c>
       <c r="Q2">
-        <v>9.646162986755371</v>
+        <v>3.356702327728271</v>
       </c>
       <c r="R2">
-        <v>7.103845596313477</v>
+        <v>0.73259496688842773</v>
       </c>
       <c r="S2">
-        <v>6.321864604949951</v>
+        <v>6.2038004398345947E-4</v>
       </c>
       <c r="T2">
-        <v>7.489950656890869</v>
+        <v>1.322306156158447</v>
       </c>
       <c r="U2">
-        <v>7.185243129730225</v>
+        <v>0.98758363723754883</v>
       </c>
       <c r="V2">
-        <v>6.933363437652588</v>
+        <v>0.69127273559570313</v>
       </c>
       <c r="W2">
-        <v>6.681993007659912</v>
+        <v>0.39433860778808588</v>
       </c>
       <c r="X2">
-        <v>6.456469058990479</v>
+        <v>0.17382192611694339</v>
       </c>
       <c r="Y2">
-        <v>6.302091121673584</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>3.052616119384766E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B3">
-        <v>2003706.25</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2003608</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2002056</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1999387.125</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1998422.5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1997940.625</v>
+        <v>2.574639162048697E-3</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -728,294 +757,294 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.959030866622925</v>
+        <v>7.1738052368164063</v>
       </c>
       <c r="O3">
-        <v>2.10657811164856</v>
+        <v>4.6849150657653809</v>
       </c>
       <c r="P3">
-        <v>1.302545070648193</v>
+        <v>2.5759832859039311</v>
       </c>
       <c r="Q3">
-        <v>0.7281743288040161</v>
+        <v>0.95107036828994751</v>
       </c>
       <c r="R3">
-        <v>0.4705007672309875</v>
+        <v>0.1944990009069443</v>
       </c>
       <c r="S3">
-        <v>0.3997220396995544</v>
+        <v>3.4465556382201612E-5</v>
       </c>
       <c r="T3">
-        <v>0.5161013603210449</v>
+        <v>0.37157794833183289</v>
       </c>
       <c r="U3">
-        <v>0.4860122203826904</v>
+        <v>0.27143833041191101</v>
       </c>
       <c r="V3">
-        <v>0.4609763622283936</v>
+        <v>0.1849224865436554</v>
       </c>
       <c r="W3">
-        <v>0.4362844228744507</v>
+        <v>9.8997026681900024E-2</v>
       </c>
       <c r="X3">
-        <v>0.4146881997585297</v>
+        <v>2.8988910838961601E-2</v>
       </c>
       <c r="Y3">
-        <v>0.3998241722583771</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>1.726215938106179E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B4">
-        <v>2006591.375</v>
+        <v>75.164398193359375</v>
       </c>
       <c r="C4">
-        <v>2005085.625</v>
+        <v>46.982898712158203</v>
       </c>
       <c r="D4">
-        <v>2005066.125</v>
+        <v>23.41651725769043</v>
       </c>
       <c r="E4">
-        <v>2000683.25</v>
+        <v>5.4796133041381836</v>
       </c>
       <c r="F4">
-        <v>2000014</v>
+        <v>0.7191087007522583</v>
       </c>
       <c r="G4">
-        <v>1999444.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>2.240774631500244</v>
+        <v>2.2407746315002441</v>
       </c>
       <c r="I4">
         <v>1.129790306091309</v>
       </c>
       <c r="J4">
-        <v>0.5693498849868774</v>
+        <v>0.56934988498687744</v>
       </c>
       <c r="K4">
         <v>0.368804931640625</v>
       </c>
       <c r="L4">
-        <v>0.1834845542907715</v>
+        <v>0.18348455429077151</v>
       </c>
       <c r="M4">
-        <v>0.07219839096069336</v>
+        <v>7.2198390960693359E-2</v>
       </c>
       <c r="N4">
         <v>12.83803749084473</v>
       </c>
       <c r="O4">
-        <v>8.686984062194824</v>
+        <v>8.6869840621948242</v>
       </c>
       <c r="P4">
-        <v>4.405914783477783</v>
+        <v>4.4059147834777832</v>
       </c>
       <c r="Q4">
         <v>1.189607977867126</v>
       </c>
       <c r="R4">
-        <v>0.2253356277942657</v>
+        <v>0.22533562779426569</v>
       </c>
       <c r="S4">
-        <v>0.004307497292757034</v>
+        <v>4.3074972927570343E-3</v>
       </c>
       <c r="T4">
-        <v>0.3282365500926971</v>
+        <v>0.32823655009269709</v>
       </c>
       <c r="U4">
-        <v>0.2238170802593231</v>
+        <v>0.22381708025932309</v>
       </c>
       <c r="V4">
         <v>0.1579315513372421</v>
       </c>
       <c r="W4">
-        <v>0.0927807092666626</v>
+        <v>9.2780709266662598E-2</v>
       </c>
       <c r="X4">
-        <v>0.0328487828373909</v>
+        <v>3.28487828373909E-2</v>
       </c>
       <c r="Y4">
-        <v>0.006601810455322266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>6.6018104553222656E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5">
-        <v>2000834.5</v>
+        <v>24.53264236450195</v>
       </c>
       <c r="C5">
-        <v>2000644.625</v>
+        <v>15.835323333740231</v>
       </c>
       <c r="D5">
-        <v>2000553.375</v>
+        <v>7.6761813163757324</v>
       </c>
       <c r="E5">
-        <v>1998840.875</v>
+        <v>1.450720429420471</v>
       </c>
       <c r="F5">
-        <v>1997506.25</v>
+        <v>9.3852579593658447E-2</v>
       </c>
       <c r="G5">
-        <v>1997004.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.3585156500339508</v>
+        <v>0.35851565003395081</v>
       </c>
       <c r="I5">
-        <v>0.2183156460523605</v>
+        <v>0.21831564605236051</v>
       </c>
       <c r="J5">
         <v>0.1059751212596893</v>
       </c>
       <c r="K5">
-        <v>0.05546875298023224</v>
+        <v>5.5468752980232239E-2</v>
       </c>
       <c r="L5">
-        <v>0.02180173248052597</v>
+        <v>2.180173248052597E-2</v>
       </c>
       <c r="M5">
-        <v>0.00583988893777132</v>
+        <v>5.8398889377713203E-3</v>
       </c>
       <c r="N5">
-        <v>1.261049509048462</v>
+        <v>3.713090181350708</v>
       </c>
       <c r="O5">
-        <v>0.7659054398536682</v>
+        <v>2.2551660537719731</v>
       </c>
       <c r="P5">
-        <v>0.2947682738304138</v>
+        <v>0.86792874336242676</v>
       </c>
       <c r="Q5">
-        <v>0.05730795487761497</v>
+        <v>0.1687400937080383</v>
       </c>
       <c r="R5">
-        <v>0.009923342615365982</v>
+        <v>2.9218729585409161E-2</v>
       </c>
       <c r="S5">
-        <v>0.000129651089082472</v>
+        <v>3.817504330072552E-4</v>
       </c>
       <c r="T5">
-        <v>0.02150707505643368</v>
+        <v>6.3326388597488403E-2</v>
       </c>
       <c r="U5">
-        <v>0.01405694615095854</v>
+        <v>4.1389897465705872E-2</v>
       </c>
       <c r="V5">
-        <v>0.008854876272380352</v>
+        <v>2.607269212603569E-2</v>
       </c>
       <c r="W5">
-        <v>0.005062696523964405</v>
+        <v>1.490682736039162E-2</v>
       </c>
       <c r="X5">
-        <v>0.002102917060256004</v>
+        <v>6.1919223517179489E-3</v>
       </c>
       <c r="Y5">
-        <v>0.0001343623007414863</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+        <v>3.9562230813317001E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6">
-        <v>2027047.875</v>
-      </c>
-      <c r="C6">
-        <v>2019291</v>
-      </c>
-      <c r="D6">
-        <v>2011222.625</v>
-      </c>
-      <c r="E6">
-        <v>2000683.25</v>
-      </c>
-      <c r="F6">
-        <v>2000014</v>
-      </c>
-      <c r="G6">
-        <v>1999470.875</v>
-      </c>
-      <c r="H6">
-        <v>2.240774631500244</v>
-      </c>
-      <c r="I6">
+      <c r="B6" s="3">
+        <v>75.164398193359375</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46.982898712158203</v>
+      </c>
+      <c r="D6" s="3">
+        <v>23.41651725769043</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5.4796133041381836</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.7191087007522583</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.5447597503662109E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2.2407746315002441</v>
+      </c>
+      <c r="I6" s="3">
         <v>1.129790306091309</v>
       </c>
-      <c r="J6">
-        <v>0.5693498849868774</v>
-      </c>
-      <c r="K6">
+      <c r="J6" s="3">
+        <v>0.56934988498687744</v>
+      </c>
+      <c r="K6" s="3">
         <v>0.368804931640625</v>
       </c>
-      <c r="L6">
-        <v>0.1834845542907715</v>
-      </c>
-      <c r="M6">
-        <v>0.07219839096069336</v>
-      </c>
-      <c r="N6">
-        <v>26.44383239746094</v>
-      </c>
-      <c r="O6">
-        <v>20.32553100585938</v>
-      </c>
-      <c r="P6">
-        <v>14.35314750671387</v>
-      </c>
-      <c r="Q6">
-        <v>9.646162986755371</v>
-      </c>
-      <c r="R6">
-        <v>7.103845596313477</v>
-      </c>
-      <c r="S6">
-        <v>6.321864604949951</v>
-      </c>
-      <c r="T6">
-        <v>7.489950656890869</v>
-      </c>
-      <c r="U6">
-        <v>7.185243129730225</v>
-      </c>
-      <c r="V6">
-        <v>6.933363437652588</v>
-      </c>
-      <c r="W6">
-        <v>6.681993007659912</v>
-      </c>
-      <c r="X6">
-        <v>6.456469058990479</v>
-      </c>
-      <c r="Y6">
-        <v>6.302091121673584</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="L6" s="3">
+        <v>0.18348455429077151</v>
+      </c>
+      <c r="M6" s="3">
+        <v>7.2198390960693359E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>21.238359451293949</v>
+      </c>
+      <c r="O6" s="3">
+        <v>14.7111873626709</v>
+      </c>
+      <c r="P6" s="3">
+        <v>8.3353328704833984</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3.356702327728271</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0.73259496688842773</v>
+      </c>
+      <c r="S6" s="3">
+        <v>4.3074972927570343E-3</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1.322306156158447</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0.98758363723754883</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.69127273559570313</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0.39433860778808588</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.17382192611694339</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>3.052616119384766E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B7">
-        <v>2002270.25</v>
+        <v>12.266322135925289</v>
       </c>
       <c r="C7">
-        <v>2002126.25</v>
+        <v>7.9176626205444336</v>
       </c>
       <c r="D7">
-        <v>2001304.5</v>
+        <v>3.838091135025024</v>
       </c>
       <c r="E7">
-        <v>1999114</v>
+        <v>0.72536027431488037</v>
       </c>
       <c r="F7">
-        <v>1997964.25</v>
+        <v>4.6926297247409821E-2</v>
       </c>
       <c r="G7">
-        <v>1997472.625</v>
+        <v>1.287319581024349E-3</v>
       </c>
       <c r="H7">
         <v>0.1792578250169754</v>
@@ -1024,350 +1053,350 @@
         <v>0.1091578230261803</v>
       </c>
       <c r="J7">
-        <v>0.05298756062984467</v>
+        <v>5.2987560629844672E-2</v>
       </c>
       <c r="K7">
-        <v>0.02773437649011612</v>
+        <v>2.7734376490116119E-2</v>
       </c>
       <c r="L7">
-        <v>0.01090086624026299</v>
+        <v>1.090086624026299E-2</v>
       </c>
       <c r="M7">
-        <v>0.00291994446888566</v>
+        <v>2.9199444688856602E-3</v>
       </c>
       <c r="N7">
-        <v>2.86966347694397</v>
+        <v>5.4434475898742676</v>
       </c>
       <c r="O7">
-        <v>2.036016702651978</v>
+        <v>3.4700403213500981</v>
       </c>
       <c r="P7">
-        <v>1.249504446983337</v>
+        <v>1.7219560146331789</v>
       </c>
       <c r="Q7">
-        <v>0.6928654909133911</v>
+        <v>0.5599052906036377</v>
       </c>
       <c r="R7">
-        <v>0.4462598860263824</v>
+        <v>0.11185887455940249</v>
       </c>
       <c r="S7">
-        <v>0.3786908686161041</v>
+        <v>2.0810800197068599E-4</v>
       </c>
       <c r="T7">
-        <v>0.4900700747966766</v>
+        <v>0.21745218336582181</v>
       </c>
       <c r="U7">
-        <v>0.461172491312027</v>
+        <v>0.15641412138938901</v>
       </c>
       <c r="V7">
-        <v>0.4371805191040039</v>
+        <v>0.1054975837469101</v>
       </c>
       <c r="W7">
-        <v>0.4135885238647461</v>
+        <v>5.6951925158500671E-2</v>
       </c>
       <c r="X7">
-        <v>0.3929731845855713</v>
+        <v>1.7590418457984921E-2</v>
       </c>
       <c r="Y7">
-        <v>0.3787878453731537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>1.0609191376715901E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B8">
-        <v>30613.466796875</v>
+        <v>26.366537094116211</v>
       </c>
       <c r="C8">
-        <v>21389.287109375</v>
+        <v>21.16902923583984</v>
       </c>
       <c r="D8">
-        <v>10516.646484375</v>
+        <v>14.575282096862789</v>
       </c>
       <c r="E8">
-        <v>3561.450439453125</v>
+        <v>4.2754735946655273</v>
       </c>
       <c r="F8">
-        <v>1525.439331054688</v>
+        <v>0.97817003726959229</v>
       </c>
       <c r="G8">
-        <v>1248.453491210938</v>
+        <v>0.62438571453094482</v>
       </c>
       <c r="H8">
         <v>1.041920065879822</v>
       </c>
       <c r="I8">
-        <v>0.7028317451477051</v>
+        <v>0.70283174514770508</v>
       </c>
       <c r="J8">
-        <v>0.4562695920467377</v>
+        <v>0.45626959204673773</v>
       </c>
       <c r="K8">
-        <v>0.2568489611148834</v>
+        <v>0.25684896111488342</v>
       </c>
       <c r="L8">
-        <v>0.06742724776268005</v>
+        <v>6.7427247762680054E-2</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>8545.890625</v>
+        <v>4.6138935089111328</v>
       </c>
       <c r="C9">
-        <v>6404.98095703125</v>
+        <v>3.839971780776978</v>
       </c>
       <c r="D9">
-        <v>3733.2705078125</v>
+        <v>2.5599241256713872</v>
       </c>
       <c r="E9">
-        <v>1232.762573242188</v>
+        <v>0.66596531867980957</v>
       </c>
       <c r="F9">
-        <v>550.6669921875</v>
+        <v>0.1552836000919342</v>
       </c>
       <c r="G9">
-        <v>370.5406188964844</v>
+        <v>8.1284999847412109E-2</v>
       </c>
       <c r="H9">
-        <v>0.1759846806526184</v>
+        <v>0.17598468065261841</v>
       </c>
       <c r="I9">
-        <v>0.0941707119345665</v>
+        <v>9.4170711934566498E-2</v>
       </c>
       <c r="J9">
-        <v>0.04323341324925423</v>
+        <v>4.3233413249254227E-2</v>
       </c>
       <c r="K9">
-        <v>0.01435147598385811</v>
+        <v>1.435147598385811E-2</v>
       </c>
       <c r="L9">
-        <v>0.003745958209037781</v>
+        <v>3.7459582090377812E-3</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B10">
-        <v>23989.03125</v>
+        <v>11.923483848571779</v>
       </c>
       <c r="C10">
-        <v>21704.357421875</v>
+        <v>4.1029200553894043</v>
       </c>
       <c r="D10">
-        <v>9455.61328125</v>
+        <v>2.6378834247589111</v>
       </c>
       <c r="E10">
-        <v>3136.26318359375</v>
+        <v>1.6122674942016599</v>
       </c>
       <c r="F10">
-        <v>1844.8310546875</v>
+        <v>1.0487358570098879</v>
       </c>
       <c r="G10">
-        <v>1474.5615234375</v>
+        <v>0.92032337188720703</v>
       </c>
       <c r="H10">
-        <v>1.605820655822754</v>
+        <v>1.6058206558227539</v>
       </c>
       <c r="I10">
-        <v>1.155309438705444</v>
+        <v>1.1553094387054439</v>
       </c>
       <c r="J10">
-        <v>0.7466700077056885</v>
+        <v>0.74667000770568848</v>
       </c>
       <c r="K10">
-        <v>0.3688483238220215</v>
+        <v>0.36884832382202148</v>
       </c>
       <c r="L10">
         <v>0.1429440975189209</v>
       </c>
       <c r="M10">
-        <v>0.03949618339538574</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>3.9496183395385742E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B11">
-        <v>8372.7470703125</v>
+        <v>2.4287014007568359</v>
       </c>
       <c r="C11">
-        <v>6819.97314453125</v>
+        <v>1.1529911756515501</v>
       </c>
       <c r="D11">
-        <v>3530.60205078125</v>
+        <v>0.59697729349136353</v>
       </c>
       <c r="E11">
-        <v>1352.830078125</v>
+        <v>0.37012395262718201</v>
       </c>
       <c r="F11">
-        <v>688.0409545898438</v>
+        <v>0.20611979067325589</v>
       </c>
       <c r="G11">
-        <v>499.1234130859375</v>
+        <v>0.1163326129317284</v>
       </c>
       <c r="H11">
-        <v>0.2992283403873444</v>
+        <v>0.29922834038734442</v>
       </c>
       <c r="I11">
-        <v>0.1941424459218979</v>
+        <v>0.19414244592189789</v>
       </c>
       <c r="J11">
-        <v>0.1168851032853127</v>
+        <v>0.11688510328531269</v>
       </c>
       <c r="K11">
-        <v>0.04881447181105614</v>
+        <v>4.8814471811056137E-2</v>
       </c>
       <c r="L11">
-        <v>0.009724259376525879</v>
+        <v>9.7242593765258789E-3</v>
       </c>
       <c r="M11">
-        <v>0.002194232307374477</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+        <v>2.194232307374477E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12">
-        <v>30613.466796875</v>
-      </c>
-      <c r="C12">
-        <v>21704.357421875</v>
-      </c>
-      <c r="D12">
-        <v>10516.646484375</v>
-      </c>
-      <c r="E12">
-        <v>3561.450439453125</v>
-      </c>
-      <c r="F12">
-        <v>1844.8310546875</v>
-      </c>
-      <c r="G12">
-        <v>1474.5615234375</v>
-      </c>
-      <c r="H12">
-        <v>1.605820655822754</v>
-      </c>
-      <c r="I12">
-        <v>1.155309438705444</v>
-      </c>
-      <c r="J12">
-        <v>0.7466700077056885</v>
-      </c>
-      <c r="K12">
-        <v>0.3688483238220215</v>
-      </c>
-      <c r="L12">
+      <c r="B12" s="3">
+        <v>26.366537094116211</v>
+      </c>
+      <c r="C12" s="3">
+        <v>21.16902923583984</v>
+      </c>
+      <c r="D12" s="3">
+        <v>14.575282096862789</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4.2754735946655273</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.0487358570098879</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.92032337188720703</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1.6058206558227539</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1.1553094387054439</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.74667000770568848</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.36884832382202148</v>
+      </c>
+      <c r="L12" s="3">
         <v>0.1429440975189209</v>
       </c>
-      <c r="M12">
-        <v>0.03949618339538574</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+      <c r="M12" s="3">
+        <v>3.9496183395385742E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B13">
-        <v>8459.318359375</v>
+        <v>3.5212974548339839</v>
       </c>
       <c r="C13">
-        <v>6612.47705078125</v>
+        <v>2.4964816570281978</v>
       </c>
       <c r="D13">
-        <v>3631.936279296875</v>
+        <v>1.578450679779053</v>
       </c>
       <c r="E13">
-        <v>1292.79638671875</v>
+        <v>0.51804465055465698</v>
       </c>
       <c r="F13">
-        <v>619.3539428710938</v>
+        <v>0.18070168793201449</v>
       </c>
       <c r="G13">
-        <v>434.83203125</v>
+        <v>9.8808802664279938E-2</v>
       </c>
       <c r="H13">
-        <v>0.2376065254211426</v>
+        <v>0.23760652542114261</v>
       </c>
       <c r="I13">
-        <v>0.1441565752029419</v>
+        <v>0.14415657520294189</v>
       </c>
       <c r="J13">
-        <v>0.08005926012992859</v>
+        <v>8.0059260129928589E-2</v>
       </c>
       <c r="K13">
-        <v>0.03158297389745712</v>
+        <v>3.1582973897457123E-2</v>
       </c>
       <c r="L13">
-        <v>0.00673510879278183</v>
+        <v>6.7351087927818298E-3</v>
       </c>
       <c r="M13">
-        <v>0.001097116153687239</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+        <v>1.0971161536872389E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14">
-        <v>194.3907623291016</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="3">
+        <v>194.39076232910159</v>
+      </c>
+      <c r="C14" s="3">
         <v>133.3813171386719</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>77.05206298828125</v>
       </c>
-      <c r="E14">
-        <v>18.51415061950684</v>
-      </c>
-      <c r="F14">
+      <c r="E14" s="3">
+        <v>18.514150619506839</v>
+      </c>
+      <c r="F14" s="3">
         <v>0.7961125373840332</v>
       </c>
-      <c r="G14">
-        <v>0.02153539657592773</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="3">
+        <v>2.1535396575927731E-2</v>
+      </c>
+      <c r="H14" s="3">
         <v>1.023346900939941</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="3">
         <v>0.3577582836151123</v>
       </c>
-      <c r="J14">
-        <v>0.03468513488769531</v>
-      </c>
-      <c r="K14">
-        <v>0.0174330472946167</v>
-      </c>
-      <c r="L14">
-        <v>0.003472805023193359</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+      <c r="J14" s="3">
+        <v>3.4685134887695313E-2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1.7433047294616699E-2</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3.4728050231933589E-3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B15">
-        <v>17.97426223754883</v>
+        <v>17.974262237548832</v>
       </c>
       <c r="C15">
-        <v>11.69316673278809</v>
+        <v>11.693166732788089</v>
       </c>
       <c r="D15">
         <v>5.874701976776123</v>
@@ -1376,267 +1405,267 @@
         <v>0.7902531623840332</v>
       </c>
       <c r="F15">
-        <v>0.005130028817802668</v>
+        <v>5.1300288178026676E-3</v>
       </c>
       <c r="G15">
-        <v>8.31196375656873E-05</v>
+        <v>8.3119637565687299E-5</v>
       </c>
       <c r="H15">
-        <v>0.01595182716846466</v>
+        <v>1.5951827168464661E-2</v>
       </c>
       <c r="I15">
-        <v>0.002639270853251219</v>
+        <v>2.6392708532512188E-3</v>
       </c>
       <c r="J15">
-        <v>0.000205983393243514</v>
+        <v>2.05983393243514E-4</v>
       </c>
       <c r="K15">
-        <v>6.143476639408618E-05</v>
+        <v>6.1434766394086182E-5</v>
       </c>
       <c r="L15">
-        <v>9.335497452411801E-06</v>
+        <v>9.3354974524118006E-6</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B16">
-        <v>3.080214977264404</v>
+        <v>3.0802149772644039</v>
       </c>
       <c r="C16">
-        <v>2.217098236083984</v>
+        <v>2.2170982360839839</v>
       </c>
       <c r="D16">
-        <v>1.416799545288086</v>
+        <v>1.4167995452880859</v>
       </c>
       <c r="E16">
-        <v>0.2515274286270142</v>
+        <v>0.25152742862701422</v>
       </c>
       <c r="F16">
-        <v>0.08507442474365234</v>
+        <v>8.5074424743652344E-2</v>
       </c>
       <c r="G16">
-        <v>0.07032120227813721</v>
+        <v>7.0321202278137207E-2</v>
       </c>
       <c r="H16">
         <v>0.1158580780029297</v>
       </c>
       <c r="I16">
-        <v>0.08469271659851074</v>
+        <v>8.4692716598510742E-2</v>
       </c>
       <c r="J16">
-        <v>0.06654059886932373</v>
+        <v>6.654059886932373E-2</v>
       </c>
       <c r="K16">
-        <v>0.05929672718048096</v>
+        <v>5.9296727180480957E-2</v>
       </c>
       <c r="L16">
-        <v>0.05253064632415771</v>
+        <v>5.2530646324157708E-2</v>
       </c>
       <c r="M16">
-        <v>0.04832220077514648</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>4.8322200775146477E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B17">
-        <v>0.5972330570220947</v>
+        <v>0.59723305702209473</v>
       </c>
       <c r="C17">
-        <v>0.4539243280887604</v>
+        <v>0.45392432808876038</v>
       </c>
       <c r="D17">
-        <v>0.2331083714962006</v>
+        <v>0.23310837149620059</v>
       </c>
       <c r="E17">
-        <v>0.08662516623735428</v>
+        <v>8.6625166237354279E-2</v>
       </c>
       <c r="F17">
-        <v>0.04389455914497375</v>
+        <v>4.3894559144973748E-2</v>
       </c>
       <c r="G17">
-        <v>0.02452315762639046</v>
+        <v>2.4523157626390461E-2</v>
       </c>
       <c r="H17">
-        <v>0.06198857724666595</v>
+        <v>6.1988577246665948E-2</v>
       </c>
       <c r="I17">
-        <v>0.04612689837813377</v>
+        <v>4.6126898378133767E-2</v>
       </c>
       <c r="J17">
-        <v>0.03639129176735878</v>
+        <v>3.639129176735878E-2</v>
       </c>
       <c r="K17">
-        <v>0.02760391682386398</v>
+        <v>2.760391682386398E-2</v>
       </c>
       <c r="L17">
-        <v>0.01984345726668835</v>
+        <v>1.984345726668835E-2</v>
       </c>
       <c r="M17">
-        <v>0.01461991108953953</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>1.461991108953953E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B18">
-        <v>0.8983200788497925</v>
+        <v>0.89832007884979248</v>
       </c>
       <c r="C18">
-        <v>0.7605264186859131</v>
+        <v>0.76052641868591309</v>
       </c>
       <c r="D18">
-        <v>0.5931743383407593</v>
+        <v>0.59317433834075928</v>
       </c>
       <c r="E18">
         <v>0.1227995157241821</v>
       </c>
       <c r="F18">
-        <v>0.08507442474365234</v>
+        <v>8.5074424743652344E-2</v>
       </c>
       <c r="G18">
-        <v>0.07032120227813721</v>
+        <v>7.0321202278137207E-2</v>
       </c>
       <c r="H18">
         <v>0.1158580780029297</v>
       </c>
       <c r="I18">
-        <v>0.08469271659851074</v>
+        <v>8.4692716598510742E-2</v>
       </c>
       <c r="J18">
-        <v>0.06654059886932373</v>
+        <v>6.654059886932373E-2</v>
       </c>
       <c r="K18">
-        <v>0.05929672718048096</v>
+        <v>5.9296727180480957E-2</v>
       </c>
       <c r="L18">
-        <v>0.05253064632415771</v>
+        <v>5.2530646324157708E-2</v>
       </c>
       <c r="M18">
-        <v>0.04832220077514648</v>
+        <v>4.8322200775146477E-2</v>
       </c>
       <c r="N18">
-        <v>0.4485063552856445</v>
+        <v>0.54439997673034668</v>
       </c>
       <c r="O18">
-        <v>0.309362530708313</v>
+        <v>0.37580204010009771</v>
       </c>
       <c r="P18">
-        <v>0.1717597246170044</v>
+        <v>0.20954322814941409</v>
       </c>
       <c r="Q18">
-        <v>0.06618285179138184</v>
+        <v>8.0603480339050293E-2</v>
       </c>
       <c r="R18">
-        <v>0.01502060890197754</v>
+        <v>1.7450213432312012E-2</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0.02912092208862305</v>
+        <v>3.6851406097412109E-2</v>
       </c>
       <c r="U18">
-        <v>0.02159059047698975</v>
+        <v>2.7791142463684079E-2</v>
       </c>
       <c r="V18">
-        <v>0.01523661613464355</v>
+        <v>1.9559621810913089E-2</v>
       </c>
       <c r="W18">
-        <v>0.008941054344177246</v>
+        <v>1.123523712158203E-2</v>
       </c>
       <c r="X18">
-        <v>0.003296375274658203</v>
+        <v>3.9609670639038086E-3</v>
       </c>
       <c r="Y18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <v>0.5263351202011108</v>
+        <v>0.52633512020111084</v>
       </c>
       <c r="C19">
-        <v>0.3798178434371948</v>
+        <v>0.37981784343719482</v>
       </c>
       <c r="D19">
-        <v>0.2074008733034134</v>
+        <v>0.20740087330341339</v>
       </c>
       <c r="E19">
-        <v>0.09394946694374084</v>
+        <v>9.3949466943740845E-2</v>
       </c>
       <c r="F19">
-        <v>0.05090417340397835</v>
+        <v>5.0904173403978348E-2</v>
       </c>
       <c r="G19">
-        <v>0.02869928628206253</v>
+        <v>2.8699286282062531E-2</v>
       </c>
       <c r="H19">
-        <v>0.06882882118225098</v>
+        <v>6.8828821182250977E-2</v>
       </c>
       <c r="I19">
-        <v>0.05352978408336639</v>
+        <v>5.3529784083366387E-2</v>
       </c>
       <c r="J19">
-        <v>0.04196493327617645</v>
+        <v>4.1964933276176453E-2</v>
       </c>
       <c r="K19">
-        <v>0.03105433098971844</v>
+        <v>3.1054330989718441E-2</v>
       </c>
       <c r="L19">
-        <v>0.02121143229305744</v>
+        <v>2.1211432293057442E-2</v>
       </c>
       <c r="M19">
-        <v>0.01580048352479935</v>
+        <v>1.580048352479935E-2</v>
       </c>
       <c r="N19">
-        <v>0.3850928246974945</v>
+        <v>0.38520494103431702</v>
       </c>
       <c r="O19">
-        <v>0.2615264356136322</v>
+        <v>0.26051750779151922</v>
       </c>
       <c r="P19">
-        <v>0.1395338922739029</v>
+        <v>0.13750758767127991</v>
       </c>
       <c r="Q19">
-        <v>0.04482899233698845</v>
+        <v>4.3699596077203751E-2</v>
       </c>
       <c r="R19">
-        <v>0.003921740688383579</v>
+        <v>4.1174753569066516E-3</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.01057482417672873</v>
+        <v>1.060017570853233E-2</v>
       </c>
       <c r="U19">
-        <v>0.005818764213472605</v>
+        <v>6.3539855182170868E-3</v>
       </c>
       <c r="V19">
-        <v>0.003013663925230503</v>
+        <v>3.62013652920723E-3</v>
       </c>
       <c r="W19">
-        <v>0.001330097555182874</v>
+        <v>1.5350198373198509E-3</v>
       </c>
       <c r="X19">
-        <v>0.0003272030153311789</v>
+        <v>3.0730804428458208E-4</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
@@ -1644,28 +1673,28 @@
         <v>2.072689294815063</v>
       </c>
       <c r="C20">
-        <v>1.258597373962402</v>
+        <v>1.2585973739624019</v>
       </c>
       <c r="D20">
-        <v>0.5798462629318237</v>
+        <v>0.57984626293182373</v>
       </c>
       <c r="E20">
-        <v>0.3162781596183777</v>
+        <v>0.31627815961837769</v>
       </c>
       <c r="F20">
-        <v>0.09521454572677612</v>
+        <v>9.5214545726776123E-2</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0.3216869235038757</v>
+        <v>0.32168692350387568</v>
       </c>
       <c r="I20">
-        <v>0.2267276644706726</v>
+        <v>0.22672766447067261</v>
       </c>
       <c r="J20">
-        <v>0.1383257508277893</v>
+        <v>0.13832575082778931</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1677,36 +1706,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B21">
-        <v>0.6166159510612488</v>
+        <v>0.61661595106124878</v>
       </c>
       <c r="C21">
-        <v>0.4836443364620209</v>
+        <v>0.48364433646202087</v>
       </c>
       <c r="D21">
-        <v>0.3142700791358948</v>
+        <v>0.31427007913589478</v>
       </c>
       <c r="E21">
         <v>0.1006647422909737</v>
       </c>
       <c r="F21">
-        <v>0.002346172230318189</v>
+        <v>2.3461722303181891E-3</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0.06919564306735992</v>
+        <v>6.9195643067359924E-2</v>
       </c>
       <c r="I21">
-        <v>0.00915970653295517</v>
+        <v>9.1597065329551697E-3</v>
       </c>
       <c r="J21">
-        <v>0.004439594224095345</v>
+        <v>4.4395942240953454E-3</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1718,21 +1747,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B22">
-        <v>0.9433035254478455</v>
+        <v>0.94330352544784546</v>
       </c>
       <c r="C22">
         <v>0.7890971302986145</v>
       </c>
       <c r="D22">
-        <v>0.5798462629318237</v>
+        <v>0.57984626293182373</v>
       </c>
       <c r="E22">
-        <v>0.2664653658866882</v>
+        <v>0.26646536588668818</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1741,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0.3029770255088806</v>
+        <v>0.30297702550888062</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1759,16 +1788,16 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0.1796738505363464</v>
+        <v>0.17967385053634641</v>
       </c>
       <c r="O22">
-        <v>0.1024823188781738</v>
+        <v>0.1027804613113403</v>
       </c>
       <c r="P22">
-        <v>0.02039819955825806</v>
+        <v>4.795759916305542E-2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.2040138244628911E-3</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -1795,21 +1824,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B23">
-        <v>0.6371212601661682</v>
+        <v>0.63712126016616821</v>
       </c>
       <c r="C23">
-        <v>0.5147944092750549</v>
+        <v>0.51479440927505493</v>
       </c>
       <c r="D23">
-        <v>0.3433551490306854</v>
+        <v>0.34335514903068542</v>
       </c>
       <c r="E23">
-        <v>0.05014454200863838</v>
+        <v>5.0144542008638382E-2</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1818,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0.04835681617259979</v>
+        <v>4.8356816172599792E-2</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1836,16 +1865,16 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0.09067833423614502</v>
+        <v>8.4514647722244263E-2</v>
       </c>
       <c r="O23">
-        <v>0.04193269088864326</v>
+        <v>3.9427280426025391E-2</v>
       </c>
       <c r="P23">
-        <v>0.001199811697006226</v>
+        <v>3.4000682644546032E-3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.2717242245562371E-5</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -1872,284 +1901,284 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B24">
-        <v>3.080214977264404</v>
-      </c>
-      <c r="C24">
-        <v>2.217098236083984</v>
-      </c>
-      <c r="D24">
-        <v>1.416799545288086</v>
-      </c>
-      <c r="E24">
-        <v>0.3162781596183777</v>
-      </c>
-      <c r="F24">
-        <v>0.09521454572677612</v>
-      </c>
-      <c r="G24">
-        <v>0.07032120227813721</v>
-      </c>
-      <c r="H24">
-        <v>0.3216869235038757</v>
-      </c>
-      <c r="I24">
-        <v>0.2267276644706726</v>
-      </c>
-      <c r="J24">
-        <v>0.1383257508277893</v>
-      </c>
-      <c r="K24">
-        <v>0.05929672718048096</v>
-      </c>
-      <c r="L24">
-        <v>0.05253064632415771</v>
-      </c>
-      <c r="M24">
-        <v>0.04832220077514648</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+      <c r="B24" s="3">
+        <v>3.0802149772644039</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.2170982360839839</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.4167995452880859</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.31627815961837769</v>
+      </c>
+      <c r="F24" s="3">
+        <v>9.5214545726776123E-2</v>
+      </c>
+      <c r="G24" s="3">
+        <v>7.0321202278137207E-2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.32168692350387568</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.22672766447067261</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.13832575082778931</v>
+      </c>
+      <c r="K24" s="3">
+        <v>5.9296727180480957E-2</v>
+      </c>
+      <c r="L24" s="3">
+        <v>5.2530646324157708E-2</v>
+      </c>
+      <c r="M24" s="3">
+        <v>4.8322200775146477E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B25">
-        <v>0.6069244742393494</v>
+        <v>0.60692447423934937</v>
       </c>
       <c r="C25">
         <v>0.4687843918800354</v>
       </c>
       <c r="D25">
-        <v>0.2736892402172089</v>
+        <v>0.27368924021720892</v>
       </c>
       <c r="E25">
-        <v>0.09364496171474457</v>
+        <v>9.3644961714744568E-2</v>
       </c>
       <c r="F25">
-        <v>0.02312036603689194</v>
+        <v>2.3120366036891941E-2</v>
       </c>
       <c r="G25">
-        <v>0.01226157881319523</v>
+        <v>1.226157881319523E-2</v>
       </c>
       <c r="H25">
-        <v>0.06559211015701294</v>
+        <v>6.5592110157012939E-2</v>
       </c>
       <c r="I25">
-        <v>0.02764330431818962</v>
+        <v>2.7643304318189621E-2</v>
       </c>
       <c r="J25">
-        <v>0.02041544392704964</v>
+        <v>2.041544392704964E-2</v>
       </c>
       <c r="K25">
-        <v>0.01380195841193199</v>
+        <v>1.380195841193199E-2</v>
       </c>
       <c r="L25">
-        <v>0.009921728633344173</v>
+        <v>9.9217286333441734E-3</v>
       </c>
       <c r="M25">
-        <v>0.007309955544769764</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+        <v>7.3099555447697639E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B26">
-        <v>0.9433035254478455</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="3">
+        <v>0.94330352544784546</v>
+      </c>
+      <c r="C26" s="3">
         <v>0.7890971302986145</v>
       </c>
-      <c r="D26">
-        <v>0.5931743383407593</v>
-      </c>
-      <c r="E26">
-        <v>0.2664653658866882</v>
-      </c>
-      <c r="F26">
-        <v>0.08507442474365234</v>
-      </c>
-      <c r="G26">
-        <v>0.07032120227813721</v>
-      </c>
-      <c r="H26">
-        <v>0.3029770255088806</v>
-      </c>
-      <c r="I26">
-        <v>0.08469271659851074</v>
-      </c>
-      <c r="J26">
-        <v>0.06654059886932373</v>
-      </c>
-      <c r="K26">
-        <v>0.05929672718048096</v>
-      </c>
-      <c r="L26">
-        <v>0.05253064632415771</v>
-      </c>
-      <c r="M26">
-        <v>0.04832220077514648</v>
-      </c>
-      <c r="N26">
-        <v>0.4485063552856445</v>
-      </c>
-      <c r="O26">
-        <v>0.309362530708313</v>
-      </c>
-      <c r="P26">
-        <v>0.1717597246170044</v>
-      </c>
-      <c r="Q26">
-        <v>0.06618285179138184</v>
-      </c>
-      <c r="R26">
-        <v>0.01502060890197754</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0.02912092208862305</v>
-      </c>
-      <c r="U26">
-        <v>0.02159059047698975</v>
-      </c>
-      <c r="V26">
-        <v>0.01523661613464355</v>
-      </c>
-      <c r="W26">
-        <v>0.008941054344177246</v>
-      </c>
-      <c r="X26">
-        <v>0.003296375274658203</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+      <c r="D26" s="3">
+        <v>0.59317433834075928</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.26646536588668818</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8.5074424743652344E-2</v>
+      </c>
+      <c r="G26" s="3">
+        <v>7.0321202278137207E-2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.30297702550888062</v>
+      </c>
+      <c r="I26" s="3">
+        <v>8.4692716598510742E-2</v>
+      </c>
+      <c r="J26" s="3">
+        <v>6.654059886932373E-2</v>
+      </c>
+      <c r="K26" s="3">
+        <v>5.9296727180480957E-2</v>
+      </c>
+      <c r="L26" s="3">
+        <v>5.2530646324157708E-2</v>
+      </c>
+      <c r="M26" s="3">
+        <v>4.8322200775146477E-2</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0.54439997673034668</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0.37580204010009771</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0.20954322814941409</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>8.0603480339050293E-2</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1.7450213432312012E-2</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>3.6851406097412109E-2</v>
+      </c>
+      <c r="U26" s="3">
+        <v>2.7791142463684079E-2</v>
+      </c>
+      <c r="V26" s="3">
+        <v>1.9559621810913089E-2</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.123523712158203E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>3.9609670639038086E-3</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B27">
-        <v>0.5817282199859619</v>
+        <v>0.58172821998596191</v>
       </c>
       <c r="C27">
-        <v>0.447306215763092</v>
+        <v>0.44730621576309199</v>
       </c>
       <c r="D27">
-        <v>0.2753779888153076</v>
+        <v>0.27537798881530762</v>
       </c>
       <c r="E27">
-        <v>0.07204701006412506</v>
+        <v>7.2047010064125061E-2</v>
       </c>
       <c r="F27">
-        <v>0.02545208670198917</v>
+        <v>2.545208670198917E-2</v>
       </c>
       <c r="G27">
-        <v>0.01434964314103127</v>
+        <v>1.434964314103127E-2</v>
       </c>
       <c r="H27">
-        <v>0.05859282240271568</v>
+        <v>5.8592822402715683E-2</v>
       </c>
       <c r="I27">
-        <v>0.0267648920416832</v>
+        <v>2.67648920416832E-2</v>
       </c>
       <c r="J27">
-        <v>0.02098246663808823</v>
+        <v>2.098246663808823E-2</v>
       </c>
       <c r="K27">
-        <v>0.01552716549485922</v>
+        <v>1.552716549485922E-2</v>
       </c>
       <c r="L27">
-        <v>0.01060571614652872</v>
+        <v>1.0605716146528721E-2</v>
       </c>
       <c r="M27">
-        <v>0.007900241762399673</v>
+        <v>7.9002417623996735E-3</v>
       </c>
       <c r="N27">
-        <v>0.2378855794668198</v>
+        <v>0.23485977947711939</v>
       </c>
       <c r="O27">
-        <v>0.1517295688390732</v>
+        <v>0.14997239410877231</v>
       </c>
       <c r="P27">
-        <v>0.07036685198545456</v>
+        <v>7.0453830063343048E-2</v>
       </c>
       <c r="Q27">
-        <v>0.02241449616849422</v>
+        <v>2.1861156448721889E-2</v>
       </c>
       <c r="R27">
-        <v>0.00196087034419179</v>
+        <v>2.0587376784533258E-3</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.005287412088364363</v>
+        <v>5.3000878542661667E-3</v>
       </c>
       <c r="U27">
-        <v>0.002909382106736302</v>
+        <v>3.176992759108543E-3</v>
       </c>
       <c r="V27">
-        <v>0.001506831962615252</v>
+        <v>1.810068264603615E-3</v>
       </c>
       <c r="W27">
-        <v>0.0006650487775914371</v>
+        <v>7.6750991865992546E-4</v>
       </c>
       <c r="X27">
-        <v>0.0001636015076655895</v>
+        <v>1.536540221422911E-4</v>
       </c>
       <c r="Y27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="3">
         <v>1.539815306663513</v>
       </c>
-      <c r="C28">
-        <v>1.455911040306091</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="3">
+        <v>1.4559110403060911</v>
+      </c>
+      <c r="D28" s="3">
         <v>1.386166095733643</v>
       </c>
-      <c r="E28">
-        <v>1.337505340576172</v>
-      </c>
-      <c r="F28">
+      <c r="E28" s="3">
+        <v>1.3375053405761721</v>
+      </c>
+      <c r="F28" s="3">
         <v>1.31172239780426</v>
       </c>
-      <c r="G28">
-        <v>1.297229766845703</v>
-      </c>
-      <c r="H28">
-        <v>1.326926231384277</v>
-      </c>
-      <c r="I28">
-        <v>1.314356446266174</v>
-      </c>
-      <c r="J28">
-        <v>1.304000020027161</v>
-      </c>
-      <c r="K28">
-        <v>1.295633316040039</v>
-      </c>
-      <c r="L28">
+      <c r="G28" s="3">
+        <v>1.2972297668457029</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1.3269262313842769</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1.3143564462661741</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1.3040000200271611</v>
+      </c>
+      <c r="K28" s="3">
+        <v>1.2956333160400391</v>
+      </c>
+      <c r="L28" s="3">
         <v>1.28966236114502</v>
       </c>
-      <c r="M28">
-        <v>1.286335110664368</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+      <c r="M28" s="3">
+        <v>1.2863351106643679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
@@ -2157,37 +2186,37 @@
         <v>0.9939618706703186</v>
       </c>
       <c r="C29">
-        <v>0.9515977501869202</v>
+        <v>0.95159775018692017</v>
       </c>
       <c r="D29">
-        <v>0.9159565567970276</v>
+        <v>0.91595655679702759</v>
       </c>
       <c r="E29">
-        <v>0.8905561566352844</v>
+        <v>0.89055615663528442</v>
       </c>
       <c r="F29">
         <v>0.8797488808631897</v>
       </c>
       <c r="G29">
-        <v>0.8745918273925781</v>
+        <v>0.87459182739257813</v>
       </c>
       <c r="H29">
-        <v>0.8836096525192261</v>
+        <v>0.88360965251922607</v>
       </c>
       <c r="I29">
         <v>0.8804020881652832</v>
       </c>
       <c r="J29">
-        <v>0.8776777386665344</v>
+        <v>0.87767773866653442</v>
       </c>
       <c r="K29">
-        <v>0.8754273653030396</v>
+        <v>0.87542736530303955</v>
       </c>
       <c r="L29">
-        <v>0.8736795783042908</v>
+        <v>0.87367957830429077</v>
       </c>
       <c r="M29">
-        <v>0.8726832270622253</v>
+        <v>0.87268322706222534</v>
       </c>
     </row>
   </sheetData>
